--- a/downloads/Trainory_Asset_Inventory.xlsx
+++ b/downloads/Trainory_Asset_Inventory.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Inventory" sheetId="1" r:id="Rd14a19674b644ebc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="2" r:id="R0f52c3b17f4d4a76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Inventory" sheetId="1" r:id="R33c9cd25aca04cc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="2" r:id="Rf3f899ae2a154cb0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -77,8 +77,14 @@
       <x:color rgb="FF1F2937"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos Display"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -103,6 +109,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF7FAFC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -202,7 +238,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="73">
+  <x:cellXfs count="80">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -366,6 +402,27 @@
     <x:xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -377,7 +434,7 @@
         <x:color rgb="FF9B1C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -387,7 +444,7 @@
         <x:color rgb="FF7A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -398,7 +455,7 @@
         <x:color rgb="FF842029"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8D7DA"/>
         </x:patternFill>
       </x:fill>
@@ -409,7 +466,7 @@
         <x:color rgb="FF664D03"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF3CD"/>
         </x:patternFill>
       </x:fill>
@@ -672,21 +729,47 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Step 2 | Inventory of systems, data, devices, and services within the initial GRC assessment scope</x:v>
-      </x:c>
-      <x:c r="B2" s="6"/>
-      <x:c r="C2" s="6"/>
-      <x:c r="D2" s="6"/>
-      <x:c r="E2" s="6"/>
-      <x:c r="F2" s="6"/>
-      <x:c r="G2" s="6"/>
-      <x:c r="H2" s="6"/>
-      <x:c r="I2" s="6"/>
-      <x:c r="J2" s="6"/>
-      <x:c r="K2" s="6"/>
-      <x:c r="L2" s="6"/>
-      <x:c r="M2" s="6"/>
-      <x:c r="N2" s="6"/>
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str">
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="str">
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="str">
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str">
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
+      <x:c r="J2" s="6" t="str">
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="str">
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
+      <x:c r="M2" s="6" t="str">
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
+      <x:c r="N2" s="6" t="str">
+        <x:v>Systems, data, devices, and services within the assessment scope</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="38" customHeight="1">
       <x:c r="A4" s="18" t="str">
@@ -1424,7 +1507,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97a261a2c2a3425a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10534a1724ef48fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1439,14 +1522,22 @@
     <x:col min="5" max="5" width="55" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>How to Read the Trainory Asset Inventory</x:v>
-      </x:c>
-      <x:c r="B1" s="3"/>
-      <x:c r="C1" s="3"/>
-      <x:c r="D1" s="3"/>
-      <x:c r="E1" s="3"/>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="79" t="str">
+        <x:v>Asset Inventory Definitions</x:v>
+      </x:c>
+      <x:c r="B1" s="79" t="str">
+        <x:v>Asset Inventory Definitions</x:v>
+      </x:c>
+      <x:c r="C1" s="79" t="str">
+        <x:v>Asset Inventory Definitions</x:v>
+      </x:c>
+      <x:c r="D1" s="79" t="str">
+        <x:v>Asset Inventory Definitions</x:v>
+      </x:c>
+      <x:c r="E1" s="79" t="str">
+        <x:v>Asset Inventory Definitions</x:v>
+      </x:c>
       <x:c r="F1" s="3"/>
     </x:row>
     <x:row r="3">
@@ -1534,10 +1625,8 @@
       <x:c r="B9" s="47" t="str">
         <x:v>How damaging unauthorized or incorrect changes would be.</x:v>
       </x:c>
-      <x:c r="D9" s="52" t="str">
-        <x:v>Interview explanation</x:v>
-      </x:c>
-      <x:c r="E9" s="52" t="str"/>
+      <x:c r="D9" s="52"/>
+      <x:c r="E9" s="52"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="50" t="str">
@@ -1546,9 +1635,7 @@
       <x:c r="B10" s="47" t="str">
         <x:v>How damaging loss of access or service would be.</x:v>
       </x:c>
-      <x:c r="D10" s="67" t="str">
-        <x:v>I created an asset inventory to establish what Trainory needs to protect before evaluating risk. I identified each asset's owner, location, sensitivity, business criticality, and confidentiality, integrity, and availability requirements. This creates the foundation for the risk assessment and control review.</x:v>
-      </x:c>
+      <x:c r="D10" s="67"/>
       <x:c r="E10" s="68"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -1583,9 +1670,9 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="D9:E9"/>
     <x:mergeCell ref="D10:E13"/>
+    <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
